--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260930.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260930.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2183,7 +2183,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3435,7 +3435,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4089,7 +4089,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4315,7 +4315,7 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15819,7 +15819,7 @@
       <c r="AD135" t="inlineStr"/>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20067,7 +20067,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20541,7 +20541,7 @@
       <c r="AD176" t="inlineStr"/>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21281,7 +21281,7 @@
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23557,7 +23557,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23909,7 +23909,7 @@
       <c r="AD205" t="inlineStr"/>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24035,7 +24035,7 @@
       <c r="AD206" t="inlineStr"/>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24161,7 +24161,7 @@
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25545,7 +25545,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25885,7 +25885,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26921,7 +26921,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27033,7 +27033,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27489,7 +27489,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27609,7 +27609,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27719,7 +27719,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28053,7 +28053,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28167,7 +28167,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28389,7 +28389,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29199,7 +29199,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29751,7 +29751,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29879,7 +29879,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30097,7 +30097,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30213,7 +30213,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30665,7 +30665,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30891,7 +30891,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31233,7 +31233,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31453,7 +31453,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31553,7 +31553,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31885,7 +31885,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32005,7 +32005,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32227,7 +32227,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32455,7 +32455,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32567,7 +32567,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32677,7 +32677,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32793,7 +32793,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32903,7 +32903,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33029,7 +33029,7 @@
       <c r="AD285" t="inlineStr"/>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33157,7 +33157,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33269,7 +33269,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33583,7 +33583,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33697,7 +33697,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33797,7 +33797,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33917,7 +33917,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34029,7 +34029,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34255,7 +34255,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34483,7 +34483,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34615,7 +34615,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34743,7 +34743,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34871,7 +34871,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34999,7 +34999,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35223,7 +35223,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35443,7 +35443,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35681,7 +35681,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35921,7 +35921,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36033,7 +36033,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36143,7 +36143,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36263,7 +36263,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36387,7 +36387,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36511,7 +36511,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36635,7 +36635,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36747,7 +36747,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36863,7 +36863,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37231,7 +37231,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37455,7 +37455,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37565,7 +37565,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37791,7 +37791,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38151,7 +38151,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38367,7 +38367,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38479,7 +38479,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38607,7 +38607,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38731,7 +38731,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38843,7 +38843,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38953,7 +38953,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39063,7 +39063,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39513,7 +39513,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39733,7 +39733,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39853,7 +39853,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39973,7 +39973,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40093,7 +40093,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40213,7 +40213,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40445,7 +40445,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40561,7 +40561,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40673,7 +40673,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40789,7 +40789,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41021,7 +41021,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41137,7 +41137,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41253,7 +41253,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41369,7 +41369,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41485,7 +41485,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41599,7 +41599,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:33</t>
+          <t>2026-09-30 15:11:03</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41715,7 +41715,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41831,7 +41831,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41947,7 +41947,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42173,7 +42173,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42619,7 +42619,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42731,7 +42731,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43099,7 +43099,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43227,7 +43227,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43339,7 +43339,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43449,7 +43449,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43559,7 +43559,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43671,7 +43671,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43783,7 +43783,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43893,7 +43893,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44119,7 +44119,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44341,7 +44341,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44451,7 +44451,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44579,7 +44579,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44691,7 +44691,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44819,7 +44819,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44931,7 +44931,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45041,7 +45041,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45151,7 +45151,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45373,7 +45373,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45483,7 +45483,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45611,7 +45611,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45723,7 +45723,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45833,7 +45833,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45943,7 +45943,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46163,7 +46163,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46273,7 +46273,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46385,7 +46385,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46513,7 +46513,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46623,7 +46623,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46733,7 +46733,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46845,7 +46845,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46955,7 +46955,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47067,7 +47067,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47195,7 +47195,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47305,7 +47305,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47417,7 +47417,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47527,7 +47527,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47637,7 +47637,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47747,7 +47747,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47847,7 +47847,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47957,7 +47957,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48057,7 +48057,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48167,7 +48167,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48295,7 +48295,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48405,7 +48405,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48515,7 +48515,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48625,7 +48625,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48735,7 +48735,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48845,7 +48845,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48955,7 +48955,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49065,7 +49065,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49175,7 +49175,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49303,7 +49303,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49415,7 +49415,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49515,7 +49515,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49625,7 +49625,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49739,7 +49739,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49849,7 +49849,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49949,7 +49949,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50173,7 +50173,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50283,7 +50283,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50395,7 +50395,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50507,7 +50507,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50745,7 +50745,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50877,7 +50877,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51009,7 +51009,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51141,7 +51141,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51265,7 +51265,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51377,7 +51377,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51477,7 +51477,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51597,7 +51597,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51713,7 +51713,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51825,7 +51825,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51947,7 +51947,7 @@
       <c r="AD450" t="inlineStr"/>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52059,7 +52059,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52169,7 +52169,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52279,7 +52279,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52389,7 +52389,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52499,7 +52499,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52627,7 +52627,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52743,7 +52743,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52853,7 +52853,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52981,7 +52981,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53237,7 +53237,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53365,7 +53365,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53477,7 +53477,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53587,7 +53587,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53715,7 +53715,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53827,7 +53827,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53939,7 +53939,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54055,7 +54055,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54279,7 +54279,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54391,7 +54391,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54503,7 +54503,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54623,7 +54623,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54733,7 +54733,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54861,7 +54861,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54981,7 +54981,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55093,7 +55093,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55205,7 +55205,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55305,7 +55305,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55421,7 +55421,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55643,7 +55643,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55753,7 +55753,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55865,7 +55865,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55977,7 +55977,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56077,7 +56077,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56187,7 +56187,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56299,7 +56299,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56409,7 +56409,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56631,7 +56631,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56741,7 +56741,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56851,7 +56851,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56961,7 +56961,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57081,7 +57081,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57205,7 +57205,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:35</t>
+          <t>2026-09-30 15:11:05</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57315,7 +57315,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57427,7 +57427,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57537,7 +57537,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57761,7 +57761,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57871,7 +57871,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57981,7 +57981,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58091,7 +58091,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58201,7 +58201,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58311,7 +58311,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58421,7 +58421,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58533,7 +58533,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58645,7 +58645,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58757,7 +58757,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58867,7 +58867,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58979,7 +58979,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59079,7 +59079,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59189,7 +59189,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59289,7 +59289,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59389,7 +59389,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59501,7 +59501,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59613,7 +59613,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59725,7 +59725,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59835,7 +59835,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59945,7 +59945,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60055,7 +60055,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60167,7 +60167,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60277,7 +60277,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60387,7 +60387,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60497,7 +60497,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60607,7 +60607,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60719,7 +60719,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60831,7 +60831,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60947,7 +60947,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61075,7 +61075,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61187,7 +61187,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61297,7 +61297,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61417,7 +61417,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61527,7 +61527,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61637,7 +61637,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61867,7 +61867,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61983,7 +61983,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62095,7 +62095,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62215,7 +62215,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62327,7 +62327,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62427,7 +62427,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62547,7 +62547,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62657,7 +62657,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62769,7 +62769,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62885,7 +62885,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62997,7 +62997,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63109,7 +63109,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63237,7 +63237,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63347,7 +63347,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63457,7 +63457,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63567,7 +63567,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63679,7 +63679,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63807,7 +63807,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63919,7 +63919,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64031,7 +64031,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64143,7 +64143,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64243,7 +64243,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64353,7 +64353,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64463,7 +64463,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64563,7 +64563,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64673,7 +64673,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64801,7 +64801,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64911,7 +64911,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65023,7 +65023,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65133,7 +65133,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65245,7 +65245,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65355,7 +65355,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65565,7 +65565,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65675,7 +65675,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65787,7 +65787,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65897,7 +65897,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66007,7 +66007,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66117,7 +66117,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66227,7 +66227,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66337,7 +66337,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66447,7 +66447,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66547,7 +66547,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66657,7 +66657,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66767,7 +66767,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66879,7 +66879,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66989,7 +66989,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67101,7 +67101,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67211,7 +67211,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67321,7 +67321,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67431,7 +67431,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67541,7 +67541,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67651,7 +67651,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67763,7 +67763,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67873,7 +67873,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67985,7 +67985,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68097,7 +68097,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68207,7 +68207,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68319,7 +68319,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68431,7 +68431,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68541,7 +68541,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68651,7 +68651,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68761,7 +68761,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68871,7 +68871,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -68971,7 +68971,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69083,7 +69083,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69193,7 +69193,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69303,7 +69303,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69431,7 +69431,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69543,7 +69543,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69655,7 +69655,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69783,7 +69783,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69895,7 +69895,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70023,7 +70023,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70151,7 +70151,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:24</t>
+          <t>2026-09-30 15:10:54</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70263,7 +70263,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70375,7 +70375,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70485,7 +70485,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70597,7 +70597,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70707,7 +70707,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70817,7 +70817,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70929,7 +70929,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71041,7 +71041,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71153,7 +71153,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71263,7 +71263,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71373,7 +71373,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71485,7 +71485,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71597,7 +71597,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71707,7 +71707,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71819,7 +71819,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71929,7 +71929,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72029,7 +72029,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72139,7 +72139,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72251,7 +72251,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72361,7 +72361,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72473,7 +72473,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72583,7 +72583,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72693,7 +72693,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72803,7 +72803,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72913,7 +72913,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73023,7 +73023,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73135,7 +73135,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73245,7 +73245,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73355,7 +73355,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73465,7 +73465,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73577,7 +73577,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73687,7 +73687,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73799,7 +73799,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73911,7 +73911,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74011,7 +74011,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74121,7 +74121,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74233,7 +74233,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74345,7 +74345,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74457,7 +74457,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74569,7 +74569,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74679,7 +74679,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74789,7 +74789,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74901,7 +74901,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75011,7 +75011,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75123,7 +75123,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75223,7 +75223,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75333,7 +75333,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75445,7 +75445,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75555,7 +75555,7 @@
       <c r="AD661" t="inlineStr"/>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:51</t>
+          <t>2026-09-30 15:11:19</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75667,7 +75667,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75779,7 +75779,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75889,7 +75889,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76001,7 +76001,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76101,7 +76101,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76201,7 +76201,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76301,7 +76301,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76413,7 +76413,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76513,7 +76513,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76623,7 +76623,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76723,7 +76723,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76835,7 +76835,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76947,7 +76947,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77059,7 +77059,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77171,7 +77171,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77271,7 +77271,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77383,7 +77383,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77493,7 +77493,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77705,7 +77705,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77805,7 +77805,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77905,7 +77905,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78005,7 +78005,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78117,7 +78117,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78229,7 +78229,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78329,7 +78329,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78439,7 +78439,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78551,7 +78551,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78663,7 +78663,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78775,7 +78775,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78887,7 +78887,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -78999,7 +78999,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79111,7 +79111,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79223,7 +79223,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79323,7 +79323,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79423,7 +79423,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79535,7 +79535,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:19</t>
+          <t>2026-09-30 15:10:46</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79635,7 +79635,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79735,7 +79735,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -79835,7 +79835,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -79945,7 +79945,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80045,7 +80045,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80155,7 +80155,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80237,7 +80237,7 @@
       <c r="AD705" t="inlineStr"/>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80319,7 +80319,7 @@
       <c r="AD706" t="inlineStr"/>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80401,7 +80401,7 @@
       <c r="AD707" t="inlineStr"/>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80483,7 +80483,7 @@
       <c r="AD708" t="inlineStr"/>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-09-30 09:58:28</t>
+          <t>2026-09-30 15:10:58</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
